--- a/Excel/FestiveCopyConfig.xlsx
+++ b/Excel/FestiveCopyConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="41">
   <si>
     <t>ID</t>
   </si>
@@ -38,6 +38,15 @@
     <t>MapName</t>
   </si>
   <si>
+    <t>FirstItemType</t>
+  </si>
+  <si>
+    <t>FirstItemIdList</t>
+  </si>
+  <si>
+    <t>FirstItemQuantity</t>
+  </si>
+  <si>
     <t>ItemType</t>
   </si>
   <si>
@@ -71,43 +80,79 @@
     <t>10,500,50,25,100,5,1,5</t>
   </si>
   <si>
+    <t>5,9,5,9,15</t>
+  </si>
+  <si>
+    <t>4111,4003,4004,4013,4014</t>
+  </si>
+  <si>
+    <t>10000,100,10,10,50</t>
+  </si>
+  <si>
     <t>节日二层</t>
   </si>
   <si>
+    <t>11000,110,11,11,55</t>
+  </si>
+  <si>
     <t>节日三层</t>
   </si>
   <si>
     <t>10,600,60,30,200,10,2,6</t>
   </si>
   <si>
+    <t>12000,120,12,12,60</t>
+  </si>
+  <si>
     <t>节日四层</t>
   </si>
   <si>
+    <t>13000,130,13,13,65</t>
+  </si>
+  <si>
     <t>节日五层</t>
   </si>
   <si>
     <t>10,700,70,35,300,15,3,7</t>
   </si>
   <si>
+    <t>14000,140,14,14,70</t>
+  </si>
+  <si>
     <t>节日六层</t>
   </si>
   <si>
+    <t>15000,150,15,15,75</t>
+  </si>
+  <si>
     <t>节日七层</t>
   </si>
   <si>
     <t>10,800,80,40,400,20,4,8</t>
   </si>
   <si>
+    <t>16000,160,16,16,80</t>
+  </si>
+  <si>
     <t>节日八层</t>
   </si>
   <si>
+    <t>17000,170,17,17,85</t>
+  </si>
+  <si>
     <t>节日九层</t>
   </si>
   <si>
     <t>10,900,90,45,500,25,5,9</t>
   </si>
   <si>
+    <t>18000,180,18,18,90</t>
+  </si>
+  <si>
     <t>节日十层</t>
+  </si>
+  <si>
+    <t>19000,190,19,19,95</t>
   </si>
 </sst>
 </file>
@@ -1080,30 +1125,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:J34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="42.8333333333333" style="3" customWidth="1"/>
-    <col min="7" max="7" width="29.875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="35.6666666666667" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.9166666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="35.6666666666667" style="3" customWidth="1"/>
+    <col min="10" max="10" width="21.9166666666667" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="F1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="F2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
@@ -1121,12 +1171,21 @@
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="H3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
@@ -1140,261 +1199,397 @@
       <c r="G4" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="H4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:7">
+        <v>11</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:7">
+        <v>15</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>10</v>
-      </c>
       <c r="F7" s="7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:7">
+        <v>15</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>11</v>
-      </c>
       <c r="G8" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:7">
+        <v>22</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:7">
+      <c r="I9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:7">
+      <c r="J10" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:7">
+        <v>27</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:7">
+        <v>32</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:7">
+        <v>32</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:7">
+        <v>37</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="5:6">
+        <v>37</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="5:9">
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
-    </row>
-    <row r="17" customHeight="1" spans="5:6">
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+    </row>
+    <row r="17" customHeight="1" spans="5:9">
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
-    </row>
-    <row r="18" customHeight="1" spans="5:6">
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+    </row>
+    <row r="18" customHeight="1" spans="5:9">
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
-    </row>
-    <row r="19" customHeight="1" spans="5:6">
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+    </row>
+    <row r="19" customHeight="1" spans="5:9">
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
-    </row>
-    <row r="20" customHeight="1" spans="5:6">
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+    </row>
+    <row r="20" customHeight="1" spans="5:9">
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
-    </row>
-    <row r="21" customHeight="1" spans="5:6">
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" customHeight="1" spans="5:9">
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
-    </row>
-    <row r="22" customHeight="1" spans="5:6">
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" customHeight="1" spans="5:9">
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
-    </row>
-    <row r="23" customHeight="1" spans="5:6">
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" customHeight="1" spans="5:9">
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
-    </row>
-    <row r="24" customHeight="1" spans="5:6">
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" customHeight="1" spans="5:9">
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
-    </row>
-    <row r="25" customHeight="1" spans="6:6">
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" customHeight="1" spans="6:9">
       <c r="F25" s="6"/>
-    </row>
-    <row r="26" customHeight="1" spans="6:6">
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" customHeight="1" spans="6:9">
       <c r="F26" s="6"/>
-    </row>
-    <row r="27" customHeight="1" spans="6:6">
+      <c r="I26" s="6"/>
+    </row>
+    <row r="27" customHeight="1" spans="6:9">
       <c r="F27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="6:6">
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" customHeight="1" spans="6:9">
       <c r="F28" s="6"/>
-    </row>
-    <row r="29" customHeight="1" spans="6:6">
+      <c r="I28" s="6"/>
+    </row>
+    <row r="29" customHeight="1" spans="6:9">
       <c r="F29" s="6"/>
-    </row>
-    <row r="30" customHeight="1" spans="6:6">
+      <c r="I29" s="6"/>
+    </row>
+    <row r="30" customHeight="1" spans="6:9">
       <c r="F30" s="6"/>
-    </row>
-    <row r="31" customHeight="1" spans="6:6">
+      <c r="I30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="6:9">
       <c r="F31" s="6"/>
-    </row>
-    <row r="32" customHeight="1" spans="6:6">
+      <c r="I31" s="6"/>
+    </row>
+    <row r="32" customHeight="1" spans="6:9">
       <c r="F32" s="6"/>
-    </row>
-    <row r="33" customHeight="1" spans="6:6">
+      <c r="I32" s="6"/>
+    </row>
+    <row r="33" customHeight="1" spans="6:9">
       <c r="F33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="6:6">
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" customHeight="1" spans="6:9">
       <c r="F34" s="1"/>
+      <c r="I34" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveCopyConfig.xlsx
+++ b/Excel/FestiveCopyConfig.xlsx
@@ -71,88 +71,88 @@
     <t>节日一层</t>
   </si>
   <si>
-    <t>5,9,5,9,15,5,5,15</t>
-  </si>
-  <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020</t>
-  </si>
-  <si>
-    <t>10,500,50,25,100,5,1,5</t>
-  </si>
-  <si>
-    <t>5,9,5,9,15</t>
-  </si>
-  <si>
-    <t>4111,4003,4004,4013,4014</t>
-  </si>
-  <si>
-    <t>10000,100,10,10,50</t>
+    <t>5,9,5,9,15,5,5,15,4</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,36</t>
+  </si>
+  <si>
+    <t>10,500,50,25,100,5,1,5,20</t>
+  </si>
+  <si>
+    <t>5,9,5,9,15,4</t>
+  </si>
+  <si>
+    <t>4111,4003,4004,4013,4014,36</t>
+  </si>
+  <si>
+    <t>10000,100,10,10,50,2</t>
   </si>
   <si>
     <t>节日二层</t>
   </si>
   <si>
-    <t>11000,110,11,11,55</t>
+    <t>11000,110,11,11,55,2</t>
   </si>
   <si>
     <t>节日三层</t>
   </si>
   <si>
-    <t>10,600,60,30,200,10,2,6</t>
-  </si>
-  <si>
-    <t>12000,120,12,12,60</t>
+    <t>10,600,60,30,200,10,2,6,30</t>
+  </si>
+  <si>
+    <t>12000,120,12,12,60,2</t>
   </si>
   <si>
     <t>节日四层</t>
   </si>
   <si>
-    <t>13000,130,13,13,65</t>
+    <t>13000,130,13,13,65,2</t>
   </si>
   <si>
     <t>节日五层</t>
   </si>
   <si>
-    <t>10,700,70,35,300,15,3,7</t>
-  </si>
-  <si>
-    <t>14000,140,14,14,70</t>
+    <t>10,700,70,35,300,15,3,7,40</t>
+  </si>
+  <si>
+    <t>14000,140,14,14,70,3</t>
   </si>
   <si>
     <t>节日六层</t>
   </si>
   <si>
-    <t>15000,150,15,15,75</t>
+    <t>15000,150,15,15,75,3</t>
   </si>
   <si>
     <t>节日七层</t>
   </si>
   <si>
-    <t>10,800,80,40,400,20,4,8</t>
-  </si>
-  <si>
-    <t>16000,160,16,16,80</t>
+    <t>10,800,80,40,400,20,4,8,50</t>
+  </si>
+  <si>
+    <t>16000,160,16,16,80,3</t>
   </si>
   <si>
     <t>节日八层</t>
   </si>
   <si>
-    <t>17000,170,17,17,85</t>
+    <t>17000,170,17,17,85,3</t>
   </si>
   <si>
     <t>节日九层</t>
   </si>
   <si>
-    <t>10,900,90,45,500,25,5,9</t>
-  </si>
-  <si>
-    <t>18000,180,18,18,90</t>
+    <t>10,900,90,45,500,25,5,9,60</t>
+  </si>
+  <si>
+    <t>18000,180,18,18,90,4</t>
   </si>
   <si>
     <t>节日十层</t>
   </si>
   <si>
-    <t>19000,190,19,19,95</t>
+    <t>19000,190,19,19,95,4</t>
   </si>
 </sst>
 </file>
@@ -1133,8 +1133,8 @@
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.6666666666667" style="3" customWidth="1"/>
-    <col min="7" max="7" width="21.9166666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="40.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="26.4166666666667" style="1" customWidth="1"/>
     <col min="8" max="8" width="21.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="35.6666666666667" style="3" customWidth="1"/>
     <col min="10" max="10" width="21.9166666666667" style="1" customWidth="1"/>

--- a/Excel/FestiveCopyConfig.xlsx
+++ b/Excel/FestiveCopyConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -77,82 +77,115 @@
     <t>4008,4003,4004,4013,4014,4011,4019,4020,36</t>
   </si>
   <si>
+    <t>10,400,40,20,80,4,1,4,10</t>
+  </si>
+  <si>
+    <t>5,9,5,9,15,4</t>
+  </si>
+  <si>
+    <t>4111,4003,4004,4013,4014,36</t>
+  </si>
+  <si>
+    <t>10000,100,10,10,50,2</t>
+  </si>
+  <si>
+    <t>节日二层</t>
+  </si>
+  <si>
+    <t>11000,110,11,11,55,2</t>
+  </si>
+  <si>
+    <t>节日三层</t>
+  </si>
+  <si>
+    <t>12000,120,12,12,60,2</t>
+  </si>
+  <si>
+    <t>节日四层</t>
+  </si>
+  <si>
+    <t>节日五层</t>
+  </si>
+  <si>
     <t>10,500,50,25,100,5,1,5,20</t>
   </si>
   <si>
-    <t>5,9,5,9,15,4</t>
-  </si>
-  <si>
-    <t>4111,4003,4004,4013,4014,36</t>
-  </si>
-  <si>
-    <t>10000,100,10,10,50,2</t>
-  </si>
-  <si>
-    <t>节日二层</t>
-  </si>
-  <si>
-    <t>11000,110,11,11,55,2</t>
-  </si>
-  <si>
-    <t>节日三层</t>
+    <t>13000,130,13,13,65,2</t>
+  </si>
+  <si>
+    <t>节日六层</t>
+  </si>
+  <si>
+    <t>节日七层</t>
+  </si>
+  <si>
+    <t>14000,140,14,14,70,3</t>
+  </si>
+  <si>
+    <t>节日八层</t>
+  </si>
+  <si>
+    <t>节日九层</t>
   </si>
   <si>
     <t>10,600,60,30,200,10,2,6,30</t>
   </si>
   <si>
-    <t>12000,120,12,12,60,2</t>
-  </si>
-  <si>
-    <t>节日四层</t>
-  </si>
-  <si>
-    <t>13000,130,13,13,65,2</t>
-  </si>
-  <si>
-    <t>节日五层</t>
+    <t>15000,150,15,15,75,3</t>
+  </si>
+  <si>
+    <t>节日十层</t>
+  </si>
+  <si>
+    <t>节日十一层</t>
+  </si>
+  <si>
+    <t>16000,160,16,16,80,3</t>
+  </si>
+  <si>
+    <t>节日十二层</t>
+  </si>
+  <si>
+    <t>节日十三层</t>
   </si>
   <si>
     <t>10,700,70,35,300,15,3,7,40</t>
   </si>
   <si>
-    <t>14000,140,14,14,70,3</t>
-  </si>
-  <si>
-    <t>节日六层</t>
-  </si>
-  <si>
-    <t>15000,150,15,15,75,3</t>
-  </si>
-  <si>
-    <t>节日七层</t>
+    <t>17000,170,17,17,85,4</t>
+  </si>
+  <si>
+    <t>节日十四层</t>
+  </si>
+  <si>
+    <t>节日十五层</t>
+  </si>
+  <si>
+    <t>18000,180,18,18,90,4</t>
+  </si>
+  <si>
+    <t>节日十六层</t>
+  </si>
+  <si>
+    <t>节日十七层</t>
   </si>
   <si>
     <t>10,800,80,40,400,20,4,8,50</t>
   </si>
   <si>
-    <t>16000,160,16,16,80,3</t>
-  </si>
-  <si>
-    <t>节日八层</t>
-  </si>
-  <si>
-    <t>17000,170,17,17,85,3</t>
-  </si>
-  <si>
-    <t>节日九层</t>
-  </si>
-  <si>
-    <t>10,900,90,45,500,25,5,9,60</t>
-  </si>
-  <si>
-    <t>18000,180,18,18,90,4</t>
-  </si>
-  <si>
-    <t>节日十层</t>
-  </si>
-  <si>
     <t>19000,190,19,19,95,4</t>
+  </si>
+  <si>
+    <t>节日十八层</t>
+  </si>
+  <si>
+    <t>节日十九层</t>
+  </si>
+  <si>
+    <t>20000,200,20,20,100,5</t>
+  </si>
+  <si>
+    <t>节日二十层</t>
   </si>
 </sst>
 </file>
@@ -1141,13 +1174,13 @@
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="F1" s="3"/>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="F2" s="3"/>
@@ -1237,7 +1270,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:10">
+    <row r="6" customHeight="1" spans="1:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1263,7 +1296,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:10">
+    <row r="7" customHeight="1" spans="1:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1289,7 +1322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:10">
+    <row r="8" customHeight="1" spans="1:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1303,24 +1336,24 @@
         <v>14</v>
       </c>
       <c r="G8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:10">
+    </row>
+    <row r="9" customHeight="1" spans="1:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
@@ -1329,50 +1362,50 @@
         <v>14</v>
       </c>
       <c r="G9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:10">
+    </row>
+    <row r="10" customHeight="1" spans="1:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:10">
+    </row>
+    <row r="11" customHeight="1" spans="1:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
@@ -1381,7 +1414,7 @@
         <v>14</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>16</v>
@@ -1390,15 +1423,15 @@
         <v>17</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
@@ -1407,7 +1440,7 @@
         <v>14</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>16</v>
@@ -1416,15 +1449,15 @@
         <v>17</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
@@ -1433,7 +1466,7 @@
         <v>14</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>16</v>
@@ -1442,15 +1475,15 @@
         <v>17</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
@@ -1459,7 +1492,7 @@
         <v>14</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>16</v>
@@ -1468,118 +1501,320 @@
         <v>17</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:10">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:10">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:10">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="8" t="s">
+      <c r="H18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="5:9">
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-    </row>
-    <row r="17" customHeight="1" spans="5:9">
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-    </row>
-    <row r="18" customHeight="1" spans="5:9">
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-    </row>
-    <row r="19" customHeight="1" spans="5:9">
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-    </row>
-    <row r="20" customHeight="1" spans="5:9">
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-    </row>
-    <row r="21" customHeight="1" spans="5:9">
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-    </row>
-    <row r="22" customHeight="1" spans="5:9">
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" customHeight="1" spans="5:9">
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-    </row>
-    <row r="24" customHeight="1" spans="5:9">
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-    </row>
-    <row r="25" customHeight="1" spans="6:9">
-      <c r="F25" s="6"/>
-      <c r="I25" s="6"/>
-    </row>
-    <row r="26" customHeight="1" spans="6:9">
+    <row r="19" customHeight="1" spans="3:10">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:10">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:10">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:10">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:10">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:10">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:10">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:10">
       <c r="F26" s="6"/>
       <c r="I26" s="6"/>
     </row>
-    <row r="27" customHeight="1" spans="6:9">
+    <row r="27" customHeight="1" spans="3:10">
       <c r="F27" s="1"/>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" customHeight="1" spans="6:9">
+    <row r="28" customHeight="1" spans="3:10">
       <c r="F28" s="6"/>
       <c r="I28" s="6"/>
     </row>
-    <row r="29" customHeight="1" spans="6:9">
+    <row r="29" customHeight="1" spans="3:10">
       <c r="F29" s="6"/>
       <c r="I29" s="6"/>
     </row>
-    <row r="30" customHeight="1" spans="6:9">
+    <row r="30" customHeight="1" spans="3:10">
       <c r="F30" s="6"/>
       <c r="I30" s="6"/>
     </row>
-    <row r="31" customHeight="1" spans="6:9">
+    <row r="31" customHeight="1" spans="3:10">
       <c r="F31" s="6"/>
       <c r="I31" s="6"/>
     </row>
-    <row r="32" customHeight="1" spans="6:9">
+    <row r="32" customHeight="1" spans="3:10">
       <c r="F32" s="6"/>
       <c r="I32" s="6"/>
     </row>

--- a/Excel/FestiveCopyConfig.xlsx
+++ b/Excel/FestiveCopyConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="76">
   <si>
     <t>ID</t>
   </si>
@@ -71,121 +71,193 @@
     <t>节日一层</t>
   </si>
   <si>
-    <t>5,9,5,9,15,5,5,15,4</t>
-  </si>
-  <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020,36</t>
-  </si>
-  <si>
-    <t>10,400,40,20,80,4,1,4,10</t>
-  </si>
-  <si>
-    <t>5,9,5,9,15,4</t>
-  </si>
-  <si>
-    <t>4111,4003,4004,4013,4014,36</t>
-  </si>
-  <si>
-    <t>10000,100,10,10,50,2</t>
+    <t>5,9,5,9,15,5,5,15,4,5</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,36,4113</t>
+  </si>
+  <si>
+    <t>10,400,40,20,80,4,1,4,10,15</t>
+  </si>
+  <si>
+    <t>5,9,5,9,15,4,5</t>
+  </si>
+  <si>
+    <t>4111,4003,4004,4013,4014,36,4113</t>
+  </si>
+  <si>
+    <t>10000,100,10,10,50,2,12</t>
   </si>
   <si>
     <t>节日二层</t>
   </si>
   <si>
-    <t>11000,110,11,11,55,2</t>
+    <t>10,400,40,20,80,4,1,4,10,30</t>
+  </si>
+  <si>
+    <t>11000,110,11,11,55,2,14</t>
   </si>
   <si>
     <t>节日三层</t>
   </si>
   <si>
-    <t>12000,120,12,12,60,2</t>
+    <t>10,400,40,20,80,4,1,4,10,45</t>
+  </si>
+  <si>
+    <t>12000,120,12,12,60,2,16</t>
   </si>
   <si>
     <t>节日四层</t>
   </si>
   <si>
+    <t>10,400,40,20,80,4,1,4,10,60</t>
+  </si>
+  <si>
+    <t>12000,120,12,12,60,2,18</t>
+  </si>
+  <si>
     <t>节日五层</t>
   </si>
   <si>
-    <t>10,500,50,25,100,5,1,5,20</t>
-  </si>
-  <si>
-    <t>13000,130,13,13,65,2</t>
+    <t>10,500,50,25,100,5,1,5,20,75</t>
+  </si>
+  <si>
+    <t>13000,130,13,13,65,2,20</t>
   </si>
   <si>
     <t>节日六层</t>
   </si>
   <si>
+    <t>10,500,50,25,100,5,1,5,20,90</t>
+  </si>
+  <si>
+    <t>13000,130,13,13,65,2,22</t>
+  </si>
+  <si>
     <t>节日七层</t>
   </si>
   <si>
-    <t>14000,140,14,14,70,3</t>
+    <t>10,500,50,25,100,5,1,5,20,105</t>
+  </si>
+  <si>
+    <t>14000,140,14,14,70,3,24</t>
   </si>
   <si>
     <t>节日八层</t>
   </si>
   <si>
+    <t>10,500,50,25,100,5,1,5,20,120</t>
+  </si>
+  <si>
+    <t>14000,140,14,14,70,3,26</t>
+  </si>
+  <si>
     <t>节日九层</t>
   </si>
   <si>
-    <t>10,600,60,30,200,10,2,6,30</t>
-  </si>
-  <si>
-    <t>15000,150,15,15,75,3</t>
+    <t>10,600,60,30,200,10,2,6,30,135</t>
+  </si>
+  <si>
+    <t>15000,150,15,15,75,3,28</t>
   </si>
   <si>
     <t>节日十层</t>
   </si>
   <si>
+    <t>10,600,60,30,200,10,2,6,30,150</t>
+  </si>
+  <si>
+    <t>15000,150,15,15,75,3,30</t>
+  </si>
+  <si>
     <t>节日十一层</t>
   </si>
   <si>
-    <t>16000,160,16,16,80,3</t>
+    <t>10,600,60,30,200,10,2,6,30,165</t>
+  </si>
+  <si>
+    <t>16000,160,16,16,80,3,32</t>
   </si>
   <si>
     <t>节日十二层</t>
   </si>
   <si>
+    <t>10,600,60,30,200,10,2,6,30,180</t>
+  </si>
+  <si>
+    <t>16000,160,16,16,80,3,34</t>
+  </si>
+  <si>
     <t>节日十三层</t>
   </si>
   <si>
-    <t>10,700,70,35,300,15,3,7,40</t>
-  </si>
-  <si>
-    <t>17000,170,17,17,85,4</t>
+    <t>10,700,70,35,300,15,3,7,40,195</t>
+  </si>
+  <si>
+    <t>17000,170,17,17,85,4,36</t>
   </si>
   <si>
     <t>节日十四层</t>
   </si>
   <si>
+    <t>10,700,70,35,300,15,3,7,40,210</t>
+  </si>
+  <si>
+    <t>17000,170,17,17,85,4,38</t>
+  </si>
+  <si>
     <t>节日十五层</t>
   </si>
   <si>
-    <t>18000,180,18,18,90,4</t>
+    <t>10,700,70,35,300,15,3,7,40,225</t>
+  </si>
+  <si>
+    <t>18000,180,18,18,90,4,40</t>
   </si>
   <si>
     <t>节日十六层</t>
   </si>
   <si>
+    <t>10,700,70,35,300,15,3,7,40,240</t>
+  </si>
+  <si>
+    <t>18000,180,18,18,90,4,42</t>
+  </si>
+  <si>
     <t>节日十七层</t>
   </si>
   <si>
-    <t>10,800,80,40,400,20,4,8,50</t>
-  </si>
-  <si>
-    <t>19000,190,19,19,95,4</t>
+    <t>10,800,80,40,400,20,4,8,50,255</t>
+  </si>
+  <si>
+    <t>19000,190,19,19,95,4,44</t>
   </si>
   <si>
     <t>节日十八层</t>
   </si>
   <si>
+    <t>10,800,80,40,400,20,4,8,50,270</t>
+  </si>
+  <si>
+    <t>19000,190,19,19,95,4,46</t>
+  </si>
+  <si>
     <t>节日十九层</t>
   </si>
   <si>
-    <t>20000,200,20,20,100,5</t>
+    <t>10,800,80,40,400,20,4,8,50,285</t>
+  </si>
+  <si>
+    <t>20000,200,20,20,100,5,48</t>
   </si>
   <si>
     <t>节日二十层</t>
+  </si>
+  <si>
+    <t>10,800,80,40,400,20,4,8,50,300</t>
+  </si>
+  <si>
+    <t>20000,200,20,20,100,5,50</t>
   </si>
 </sst>
 </file>
@@ -1310,7 +1382,7 @@
         <v>14</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>16</v>
@@ -1319,7 +1391,7 @@
         <v>17</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:10">
@@ -1327,7 +1399,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>13</v>
@@ -1336,7 +1408,7 @@
         <v>14</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>16</v>
@@ -1345,7 +1417,7 @@
         <v>17</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:10">
@@ -1353,7 +1425,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
@@ -1362,7 +1434,7 @@
         <v>14</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>16</v>
@@ -1371,7 +1443,7 @@
         <v>17</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:10">
@@ -1379,7 +1451,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
@@ -1388,7 +1460,7 @@
         <v>14</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>16</v>
@@ -1397,7 +1469,7 @@
         <v>17</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:10">
@@ -1405,7 +1477,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
@@ -1414,7 +1486,7 @@
         <v>14</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>16</v>
@@ -1423,7 +1495,7 @@
         <v>17</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:10">
@@ -1431,7 +1503,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
@@ -1440,7 +1512,7 @@
         <v>14</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>16</v>
@@ -1449,7 +1521,7 @@
         <v>17</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:10">
@@ -1457,7 +1529,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
@@ -1466,7 +1538,7 @@
         <v>14</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>16</v>
@@ -1475,7 +1547,7 @@
         <v>17</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:10">
@@ -1483,7 +1555,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
@@ -1492,7 +1564,7 @@
         <v>14</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>16</v>
@@ -1501,7 +1573,7 @@
         <v>17</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:10">
@@ -1509,7 +1581,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
@@ -1518,7 +1590,7 @@
         <v>14</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>16</v>
@@ -1527,7 +1599,7 @@
         <v>17</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:10">
@@ -1535,7 +1607,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
@@ -1544,7 +1616,7 @@
         <v>14</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>16</v>
@@ -1553,7 +1625,7 @@
         <v>17</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:10">
@@ -1561,7 +1633,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>13</v>
@@ -1570,7 +1642,7 @@
         <v>14</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>16</v>
@@ -1579,7 +1651,7 @@
         <v>17</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:10">
@@ -1587,7 +1659,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>13</v>
@@ -1596,7 +1668,7 @@
         <v>14</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>16</v>
@@ -1605,7 +1677,7 @@
         <v>17</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:10">
@@ -1613,7 +1685,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>13</v>
@@ -1622,7 +1694,7 @@
         <v>14</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>16</v>
@@ -1631,7 +1703,7 @@
         <v>17</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:10">
@@ -1639,7 +1711,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
@@ -1648,7 +1720,7 @@
         <v>14</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>16</v>
@@ -1657,7 +1729,7 @@
         <v>17</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:10">
@@ -1665,7 +1737,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
@@ -1674,7 +1746,7 @@
         <v>14</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>16</v>
@@ -1683,7 +1755,7 @@
         <v>17</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:10">
@@ -1691,7 +1763,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>13</v>
@@ -1700,7 +1772,7 @@
         <v>14</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>16</v>
@@ -1709,7 +1781,7 @@
         <v>17</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:10">
@@ -1717,7 +1789,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>13</v>
@@ -1726,7 +1798,7 @@
         <v>14</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>16</v>
@@ -1735,7 +1807,7 @@
         <v>17</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:10">
@@ -1743,7 +1815,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>13</v>
@@ -1752,7 +1824,7 @@
         <v>14</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>16</v>
@@ -1761,7 +1833,7 @@
         <v>17</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:10">
@@ -1769,7 +1841,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>13</v>
@@ -1778,7 +1850,7 @@
         <v>14</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>16</v>
@@ -1787,7 +1859,7 @@
         <v>17</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:10">

--- a/Excel/FestiveCopyConfig.xlsx
+++ b/Excel/FestiveCopyConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="108">
   <si>
     <t>ID</t>
   </si>
@@ -258,6 +258,102 @@
   </si>
   <si>
     <t>20000,200,20,20,100,5,50</t>
+  </si>
+  <si>
+    <t>节日二一层</t>
+  </si>
+  <si>
+    <t>4008,4003,4004,4013,4014,4011,4019,4020,36,4114</t>
+  </si>
+  <si>
+    <t>10,600,60,30,200,10,2,6,30,40</t>
+  </si>
+  <si>
+    <t>4111,4003,4004,4013,4014,36,4114</t>
+  </si>
+  <si>
+    <t>16000,160,16,16,80,3,6</t>
+  </si>
+  <si>
+    <t>节日二二层</t>
+  </si>
+  <si>
+    <t>10,600,60,30,200,10,2,6,30,50</t>
+  </si>
+  <si>
+    <t>16000,160,16,16,80,3,7</t>
+  </si>
+  <si>
+    <t>节日二三层</t>
+  </si>
+  <si>
+    <t>10,700,70,35,300,15,3,7,40,60</t>
+  </si>
+  <si>
+    <t>17000,170,17,17,85,4,8</t>
+  </si>
+  <si>
+    <t>节日二四层</t>
+  </si>
+  <si>
+    <t>10,700,70,35,300,15,3,7,40,70</t>
+  </si>
+  <si>
+    <t>17000,170,17,17,85,4,9</t>
+  </si>
+  <si>
+    <t>节日二五层</t>
+  </si>
+  <si>
+    <t>10,700,70,35,300,15,3,7,40,80</t>
+  </si>
+  <si>
+    <t>18000,180,18,18,90,4,10</t>
+  </si>
+  <si>
+    <t>节日二六层</t>
+  </si>
+  <si>
+    <t>10,700,70,35,300,15,3,7,40,90</t>
+  </si>
+  <si>
+    <t>18000,180,18,18,90,4,11</t>
+  </si>
+  <si>
+    <t>节日二七层</t>
+  </si>
+  <si>
+    <t>10,800,80,40,400,20,4,8,50,100</t>
+  </si>
+  <si>
+    <t>19000,190,19,19,95,4,12</t>
+  </si>
+  <si>
+    <t>节日二八层</t>
+  </si>
+  <si>
+    <t>10,800,80,40,400,20,4,8,50,110</t>
+  </si>
+  <si>
+    <t>19000,190,19,19,95,4,13</t>
+  </si>
+  <si>
+    <t>节日二九层</t>
+  </si>
+  <si>
+    <t>10,800,80,40,400,20,4,8,50,120</t>
+  </si>
+  <si>
+    <t>20000,200,20,20,100,5,14</t>
+  </si>
+  <si>
+    <t>节日三十层</t>
+  </si>
+  <si>
+    <t>10,800,80,40,400,20,4,8,50,130</t>
+  </si>
+  <si>
+    <t>20000,200,20,20,100,5,15</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1326,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1867,36 +1963,264 @@
       <c r="I26" s="6"/>
     </row>
     <row r="27" customHeight="1" spans="3:10">
-      <c r="F27" s="1"/>
-      <c r="I27" s="1"/>
+      <c r="C27" s="1">
+        <v>21</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="28" customHeight="1" spans="3:10">
-      <c r="F28" s="6"/>
-      <c r="I28" s="6"/>
+      <c r="C28" s="1">
+        <v>22</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="29" customHeight="1" spans="3:10">
-      <c r="F29" s="6"/>
-      <c r="I29" s="6"/>
+      <c r="C29" s="1">
+        <v>23</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="30" customHeight="1" spans="3:10">
-      <c r="F30" s="6"/>
-      <c r="I30" s="6"/>
+      <c r="C30" s="1">
+        <v>24</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="31" customHeight="1" spans="3:10">
-      <c r="F31" s="6"/>
-      <c r="I31" s="6"/>
+      <c r="C31" s="1">
+        <v>25</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="32" customHeight="1" spans="3:10">
-      <c r="F32" s="6"/>
-      <c r="I32" s="6"/>
-    </row>
-    <row r="33" customHeight="1" spans="6:9">
-      <c r="F33" s="1"/>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="6:9">
-      <c r="F34" s="1"/>
-      <c r="I34" s="1"/>
+      <c r="C32" s="1">
+        <v>26</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:10">
+      <c r="C33" s="1">
+        <v>27</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:10">
+      <c r="C34" s="1">
+        <v>28</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:10">
+      <c r="C35" s="1">
+        <v>29</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:10">
+      <c r="C36" s="1">
+        <v>30</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>107</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveCopyConfig.xlsx
+++ b/Excel/FestiveCopyConfig.xlsx
@@ -263,97 +263,97 @@
     <t>节日二一层</t>
   </si>
   <si>
-    <t>4008,4003,4004,4013,4014,4011,4019,4020,36,4114</t>
-  </si>
-  <si>
-    <t>10,600,60,30,200,10,2,6,30,40</t>
-  </si>
-  <si>
-    <t>4111,4003,4004,4013,4014,36,4114</t>
-  </si>
-  <si>
-    <t>16000,160,16,16,80,3,6</t>
+    <t>4008,4003,4004,4013,4014,4026,4038,4020,54,4114</t>
+  </si>
+  <si>
+    <t>10,900,90,45,500,10,5,9,10,40</t>
+  </si>
+  <si>
+    <t>4111,4003,4004,4013,4014,54,4114</t>
+  </si>
+  <si>
+    <t>21000,210,21,21,105,3,6</t>
   </si>
   <si>
     <t>节日二二层</t>
   </si>
   <si>
-    <t>10,600,60,30,200,10,2,6,30,50</t>
-  </si>
-  <si>
-    <t>16000,160,16,16,80,3,7</t>
+    <t>10,900,90,45,500,11,6,9,15,50</t>
+  </si>
+  <si>
+    <t>22000,220,22,22,110,3,7</t>
   </si>
   <si>
     <t>节日二三层</t>
   </si>
   <si>
-    <t>10,700,70,35,300,15,3,7,40,60</t>
-  </si>
-  <si>
-    <t>17000,170,17,17,85,4,8</t>
+    <t>10,900,90,45,500,12,7,9,20,60</t>
+  </si>
+  <si>
+    <t>23000,230,23,23,115,4,8</t>
   </si>
   <si>
     <t>节日二四层</t>
   </si>
   <si>
-    <t>10,700,70,35,300,15,3,7,40,70</t>
-  </si>
-  <si>
-    <t>17000,170,17,17,85,4,9</t>
+    <t>10,900,90,45,500,13,8,9,25,70</t>
+  </si>
+  <si>
+    <t>24000,240,24,24,120,4,9</t>
   </si>
   <si>
     <t>节日二五层</t>
   </si>
   <si>
-    <t>10,700,70,35,300,15,3,7,40,80</t>
-  </si>
-  <si>
-    <t>18000,180,18,18,90,4,10</t>
+    <t>10,900,90,45,500,14,9,9,30,80</t>
+  </si>
+  <si>
+    <t>25000,250,25,25,125,5,10</t>
   </si>
   <si>
     <t>节日二六层</t>
   </si>
   <si>
-    <t>10,700,70,35,300,15,3,7,40,90</t>
-  </si>
-  <si>
-    <t>18000,180,18,18,90,4,11</t>
+    <t>10,1000,100,50,600,15,10,10,35,90</t>
+  </si>
+  <si>
+    <t>26000,260,26,26,130,5,11</t>
   </si>
   <si>
     <t>节日二七层</t>
   </si>
   <si>
-    <t>10,800,80,40,400,20,4,8,50,100</t>
-  </si>
-  <si>
-    <t>19000,190,19,19,95,4,12</t>
+    <t>10,1000,100,50,600,16,11,10,40,100</t>
+  </si>
+  <si>
+    <t>27000,270,27,27,135,6,12</t>
   </si>
   <si>
     <t>节日二八层</t>
   </si>
   <si>
-    <t>10,800,80,40,400,20,4,8,50,110</t>
-  </si>
-  <si>
-    <t>19000,190,19,19,95,4,13</t>
+    <t>10,1000,100,50,600,17,12,10,45,110</t>
+  </si>
+  <si>
+    <t>28000,280,28,28,140,6,13</t>
   </si>
   <si>
     <t>节日二九层</t>
   </si>
   <si>
-    <t>10,800,80,40,400,20,4,8,50,120</t>
-  </si>
-  <si>
-    <t>20000,200,20,20,100,5,14</t>
+    <t>10,1000,100,50,600,18,13,10,50,120</t>
+  </si>
+  <si>
+    <t>29000,290,29,29,145,7,14</t>
   </si>
   <si>
     <t>节日三十层</t>
   </si>
   <si>
-    <t>10,800,80,40,400,20,4,8,50,130</t>
-  </si>
-  <si>
-    <t>20000,200,20,20,100,5,15</t>
+    <t>10,1000,100,50,600,19,14,10,55,130</t>
+  </si>
+  <si>
+    <t>30000,300,30,30,150,7,15</t>
   </si>
 </sst>
 </file>
